--- a/chronogrammes/chronogramme_prs2.xlsx
+++ b/chronogrammes/chronogramme_prs2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="296">
   <si>
     <t>PRS 2.0 — Module 1 : socle transversal et dossiers de planification (Gantt hebdomadaire)</t>
   </si>
@@ -556,12 +556,6 @@
     <t>M10</t>
   </si>
   <si>
-    <t>M11</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
     <t>G01</t>
   </si>
   <si>
@@ -646,7 +640,7 @@
     <t>J8</t>
   </si>
   <si>
-    <t>Découpage PROPOSÉ — à valider.</t>
+    <t>Un mois, durée inchangée : le pilote n'a arbitré que les modules 2, 3 et 4 le 26/08. À revoir si la compression des trois modules reporte de la charge sur la recette globale.</t>
   </si>
   <si>
     <t>PRS 2.0 — Jalons</t>
@@ -3044,7 +3038,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3058,10 +3052,10 @@
     <col min="11" max="11" width="7" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
     <col min="13" max="13" width="60" customWidth="1"/>
-    <col min="14" max="25" width="4.4" customWidth="1"/>
+    <col min="14" max="23" width="4.4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
@@ -3087,10 +3081,8 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>169</v>
       </c>
@@ -3116,10 +3108,8 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -3189,14 +3179,8 @@
       <c r="W3" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -3240,24 +3224,16 @@
         <f>EDATE(Parametres!$B$2,9)</f>
         <v>46463</v>
       </c>
-      <c r="X4" s="5">
-        <f>EDATE(Parametres!$B$2,10)</f>
-        <v>46494</v>
-      </c>
-      <c r="Y4" s="5">
-        <f>EDATE(Parametres!$B$2,11)</f>
-        <v>46524</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>184</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>92</v>
@@ -3289,7 +3265,7 @@
         <v>36</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
@@ -3298,15 +3274,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>188</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>92</v>
@@ -3329,7 +3305,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>35</v>
@@ -3338,20 +3314,20 @@
         <v>35</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P6" s="14"/>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>192</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>92</v>
@@ -3367,23 +3343,23 @@
         <v>46286</v>
       </c>
       <c r="H7" s="12">
-        <f>Parametres!$B$2+182</f>
-        <v>46372</v>
+        <f>Parametres!$B$2+156</f>
+        <v>46346</v>
       </c>
       <c r="I7" s="9">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P7" s="14"/>
       <c r="Q7" s="24"/>
@@ -3392,15 +3368,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>92</v>
@@ -3412,44 +3388,44 @@
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <f>Parametres!$B$2+183</f>
-        <v>46373</v>
+        <f>Parametres!$B$2+159</f>
+        <v>46349</v>
       </c>
       <c r="H8" s="12">
-        <f>Parametres!$B$2+272</f>
-        <v>46462</v>
+        <f>Parametres!$B$2+219</f>
+        <v>46409</v>
       </c>
       <c r="I8" s="9">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M8" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="P8" s="14"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="P8" s="14"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>92</v>
@@ -3461,43 +3437,43 @@
         <v>0</v>
       </c>
       <c r="G9" s="12">
-        <f>Parametres!$B$2+273</f>
-        <v>46463</v>
+        <f>Parametres!$B$2+222</f>
+        <v>46412</v>
       </c>
       <c r="H9" s="12">
-        <f>Parametres!$B$2+333</f>
-        <v>46523</v>
+        <f>Parametres!$B$2+268</f>
+        <v>46458</v>
       </c>
       <c r="I9" s="9">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="P9" s="14"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="P9" s="14"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>92</v>
@@ -3509,30 +3485,31 @@
         <v>0</v>
       </c>
       <c r="G10" s="12">
-        <f>Parametres!$B$2+334</f>
-        <v>46524</v>
+        <f>Parametres!$B$2+271</f>
+        <v>46461</v>
       </c>
       <c r="H10" s="12">
-        <f>Parametres!$B$2+364</f>
-        <v>46554</v>
+        <f>Parametres!$B$2+303</f>
+        <v>46493</v>
       </c>
       <c r="I10" s="9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P10" s="14"/>
-      <c r="Y10" s="25" t="s">
+      <c r="V10" s="24"/>
+      <c r="W10" s="25" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3586,8 +3563,8 @@
   </sheetData>
   <autoFilter ref="A3:M10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3612,7 +3589,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3622,93 +3599,93 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="32">
         <f>Parametres!$B$2+8</f>
         <v>46198</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="32">
         <f>Parametres!$B$2+40</f>
         <v>46230</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" s="32">
         <f>Parametres!$B$2+63</f>
         <v>46253</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C7" s="32">
         <f>Parametres!$B$2+93</f>
@@ -3718,7 +3695,7 @@
         <v>140</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>35</v>
@@ -3726,20 +3703,20 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C8" s="32">
-        <f>Parametres!$B$2+182</f>
-        <v>46372</v>
+        <f>Parametres!$B$2+156</f>
+        <v>46346</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>140</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
@@ -3747,20 +3724,20 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C9" s="32">
-        <f>Parametres!$B$2+272</f>
-        <v>46462</v>
+        <f>Parametres!$B$2+219</f>
+        <v>46409</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>140</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>35</v>
@@ -3768,20 +3745,20 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C10" s="32">
-        <f>Parametres!$B$2+333</f>
-        <v>46523</v>
+        <f>Parametres!$B$2+268</f>
+        <v>46458</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>140</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>35</v>
@@ -3789,20 +3766,20 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C11" s="32">
-        <f>Parametres!$B$2+364</f>
-        <v>46554</v>
+        <f>Parametres!$B$2+303</f>
+        <v>46493</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>140</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>35</v>
@@ -3829,73 +3806,73 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="34">
         <v>46190</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B3" s="36">
         <v>46260</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B4" s="36">
         <v>46283</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>253</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="37" t="s">
         <v>256</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B7" s="35" t="s">
         <v>92</v>
@@ -3917,7 +3894,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>35</v>
@@ -3928,198 +3905,198 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B10" s="35">
         <v>26</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>263</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" s="37" t="s">
         <v>266</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B13" s="35">
         <v>3</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B14" s="35">
         <v>3</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="37" t="s">
         <v>273</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="37" t="s">
         <v>276</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="37" t="s">
         <v>279</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="40"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="40"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B24" s="40"/>
       <c r="C24" s="40"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="40"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" s="40"/>
       <c r="C26" s="40"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="40" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B28" s="40"/>
       <c r="C28" s="40"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="40" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="40"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="40" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B30" s="40"/>
       <c r="C30" s="40"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="40" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="40"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B32" s="40"/>
       <c r="C32" s="40"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="40"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="40" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B34" s="40"/>
       <c r="C34" s="40"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="40"/>

--- a/chronogrammes/chronogramme_prs2.xlsx
+++ b/chronogrammes/chronogramme_prs2.xlsx
@@ -109,10 +109,10 @@
     <t>A01</t>
   </si>
   <si>
-    <t>Socle applicatif : authentification, guards, habilitations par profil</t>
-  </si>
-  <si>
-    <t>core/auth (service de session, guard, service de permissions), services CRUD génériques</t>
+    <t>Socle d'authentification et d'habilitations</t>
+  </si>
+  <si>
+    <t>Connexion, contrôle d'accès par profil et par entité, socle commun d'appel à l'API</t>
   </si>
   <si>
     <t>Mr Lanto</t>
@@ -133,10 +133,10 @@
     <t>A02</t>
   </si>
   <si>
-    <t>Circuit d'instruction de bout en bout : dépôt → réception → dispatch → examen → PV</t>
-  </si>
-  <si>
-    <t>Moteur de workflow partagé + écrans des 6 profils du circuit</t>
+    <t>Circuit d'instruction d'un dossier, du dépôt au procès-verbal</t>
+  </si>
+  <si>
+    <t>Enchaînement dépôt → réception → affectation → examen → procès-verbal, et les écrans des six profils qui l'exercent</t>
   </si>
   <si>
     <t>Mr Mathieu</t>
@@ -148,10 +148,10 @@
     <t>A03</t>
   </si>
   <si>
-    <t>Demandes de retrait de dossier et décisions Président / Chef de commission</t>
-  </si>
-  <si>
-    <t>Écrans de demande (PRMP) et de validation (P/CC), garde « avant PV signé »</t>
+    <t>Retrait d'un dossier et décision du contrôleur</t>
+  </si>
+  <si>
+    <t>Écran de demande pour l'autorité contractante, écran de décision pour le Président et le Chef de commission, retrait bloqué dès la signature du procès-verbal</t>
   </si>
   <si>
     <t>features/circuit/retraits-validation.ts créé le 18/06 ; features/cc/retraits-decision.ts et features/prmp/retraits.ts au commit initial ; règle « retrait impossible dès PV_SIGNE » (409) — commits du 23/06 « message liste vide explicite + erreur 409 dédiée »</t>
@@ -160,10 +160,10 @@
     <t>A04</t>
   </si>
   <si>
-    <t>Rectification PRMP et navette avec le vérificateur</t>
-  </si>
-  <si>
-    <t>Statut EN_ATTENTE_DECISION_PRMP bout-en-bout, écrans « Dossiers à rectifier » et « En attente de rectification »</t>
+    <t>Rectification par l'autorité contractante et navette de vérification</t>
+  </si>
+  <si>
+    <t>Renvoi d'un dossier pour rectification, fil des échanges entre le vérificateur et l'autorité contractante, reprise de l'instruction après correction</t>
   </si>
   <si>
     <t>12 commits du 19/06 (« statut EN_ATTENTE_DECISION_PRMP (obs non levées) bout-en-bout », « resoumission après rectification ») ; création de features/prmp/dossiers-a-rectifier.ts et features/verificateur/en-attente-prmp.ts le 19/06</t>
@@ -172,10 +172,10 @@
     <t>A05</t>
   </si>
   <si>
-    <t>Lettre de renvoi et profil Assistant contrôleur</t>
-  </si>
-  <si>
-    <t>Alternative PV / lettre de renvoi, page « à signer », domaine ASSISTANT_CONTROLEUR</t>
+    <t>Lettre de renvoi et intervention de l'assistant contrôleur</t>
+  </si>
+  <si>
+    <t>Seconde issue de l'examen à côté du procès-verbal : rédaction, mise à la signature et consultation de la lettre de renvoi</t>
   </si>
   <si>
     <t>J1</t>
@@ -190,10 +190,10 @@
     <t>A06</t>
   </si>
   <si>
-    <t>Design system et migration visuelle de l'ensemble des écrans</t>
-  </si>
-  <si>
-    <t>src/styles/_design-system.scss + migration des écrans de tous les profils</t>
+    <t>Charte graphique et harmonisation de tous les écrans</t>
+  </si>
+  <si>
+    <t>Jeu commun de composants, de couleurs et de typographies, appliqué aux écrans des neuf espaces de travail</t>
   </si>
   <si>
     <t>Mr Christian</t>
@@ -208,7 +208,7 @@
     <t>Compteurs de menu et tableaux de bord par profil</t>
   </si>
   <si>
-    <t>Badges de comptage des 6 menus, tableau de bord KPI, écran de rapports</t>
+    <t>Nombre de dossiers en attente affiché sur chaque entrée de menu, tableau de bord des indicateurs et écran de rapports</t>
   </si>
   <si>
     <t>13 commits du 29/06 (« compteurs du menu PRMP / Vérificateur / Secrétaire », « compteurs scopés par localité pour le CC ») ; features/pilotage/{kpi-dashboard,rapports-page}.ts et shared/dashboard/dashboard-shell.ts ; endpoint agrégé GET /api/kpis/badges livré au commit fad4ca7</t>
@@ -217,10 +217,10 @@
     <t>A08</t>
   </si>
   <si>
-    <t>Référentiels administrables (entités, PRMP, UGPM, pièces, modes de passation)</t>
-  </si>
-  <si>
-    <t>21 écrans CRUD d'administration pilotés par configuration</t>
+    <t>Administration des référentiels</t>
+  </si>
+  <si>
+    <t>Écrans de gestion des entités contractantes, des autorités de passation, des unités de gestion, des pièces exigées et des modes de passation</t>
   </si>
   <si>
     <t>features/admin/admin-resources.config.ts (~600 lignes) et admin.routes.ts (21 `loadComponent`) ; ugpm-admin.ts créé le 06/07 ; controleur-admin.ts, prmp-admin.ts, inscriptions-admin.ts, prmp-pieces-admin.ts, ugpm-pieces-admin.ts, dmc-mapping-admin.ts créés le 16/07</t>
@@ -229,10 +229,10 @@
     <t>A09</t>
   </si>
   <si>
-    <t>Saisie du plan de passation : grille partagée, import PDF, dates prévisionnelles CAPM</t>
-  </si>
-  <si>
-    <t>shared/prmp/{ppm-saisie-grid,ppm-form-factory,ppm-marches-table}.ts, import PDF avec revue ligne à ligne</t>
+    <t>Saisie du plan de passation et reprise automatique du document PDF</t>
+  </si>
+  <si>
+    <t>Grille de saisie des lignes de marché, import d'un plan au format PDF avec revue ligne à ligne, calendrier prévisionnel par processus de passation</t>
   </si>
   <si>
     <t>20 commits du 23/06 (dates prévisionnelles par marché, référentiel CAPM, cohérence chronologique) ; shared/prmp/ppm-marches-table.ts créé le 05/07 ; ppm-form-factory.ts et ppm-saisie-grid.ts créés le 23/07 (« grille de saisie riche partagée », « soumettre consomme la grille partagée ») ; UI d'import .xlsx retirée volontairement le 22/07</t>
@@ -241,10 +241,10 @@
     <t>A10</t>
   </si>
   <si>
-    <t>Familles de dossier DDP / DMC / DDM et référentiel des sous-types</t>
-  </si>
-  <si>
-    <t>Choix de famille au dépôt, sous-type dérivé serveur pour DDP, points de contrôle par sous-type</t>
+    <t>Typologie des dossiers : familles et sous-types</t>
+  </si>
+  <si>
+    <t>Choix de la famille au dépôt (planification, mise en concurrence, marché), sous-type déterminé par le serveur, grille de points de contrôle propre à chaque sous-type</t>
   </si>
   <si>
     <t>A08, A09</t>
@@ -256,10 +256,10 @@
     <t>A11</t>
   </si>
   <si>
-    <t>Entités contractantes : création à l'import, rattachements, localité dérivée</t>
-  </si>
-  <si>
-    <t>Panneau de résolution d'entité au PDF, écran « Rattachements en attente » (Admin)</t>
+    <t>Rattachement de l'entité contractante au dépôt d'un dossier</t>
+  </si>
+  <si>
+    <t>Reconnaissance ou création de l'entité au moment de l'import, approbation par l'administrateur, localité du dossier déduite de l'entité</t>
   </si>
   <si>
     <t>20 commits le 26/07/2026 (dimanche) : « création d'une entité contractante à l'import », « écran Rattachements en attente », « localité de l'entité → localité du dossier dérivée » ; features/admin/rattachements-admin.ts créé le 26/07</t>
@@ -268,10 +268,10 @@
     <t>A12</t>
   </si>
   <si>
-    <t>Écrans « Mes dossiers » par profil et classement des dossiers</t>
-  </si>
-  <si>
-    <t>Files de travail Président, CC, Secrétaire et Membre ; cartes « Dispatchs par contrôleur »</t>
+    <t>Files de travail « Mes dossiers » de chaque profil</t>
+  </si>
+  <si>
+    <t>Écran unique par profil regroupant les dossiers à traiter, classés par étape ; vue de la charge par contrôleur pour le Président</t>
   </si>
   <si>
     <t>A10, A11</t>
@@ -286,10 +286,10 @@
     <t>A13</t>
   </si>
   <si>
-    <t>Chantier parallèle et attente backend (interruption)</t>
-  </si>
-  <si>
-    <t>aucun livrable sur ce dépôt</t>
+    <t>Interruption : chantier parallèle et attente du backend</t>
+  </si>
+  <si>
+    <t>Aucun — période sans production sur ce dépôt</t>
   </si>
   <si>
     <t>Mr Lanto, Mr Mathieu, Mr Christian</t>
@@ -301,10 +301,10 @@
     <t>A14</t>
   </si>
   <si>
-    <t>Délégation ascendante et mandats PRMP</t>
-  </si>
-  <si>
-    <t>Permissions pilotées par t_delegation_profil, écran des mandats, bannière de vacance</t>
+    <t>Délégation ascendante et mandats des autorités de passation</t>
+  </si>
+  <si>
+    <t>Exercice des tâches d'un profil subordonné par son supérieur, journal des mandats et signalement des périodes de vacance</t>
   </si>
   <si>
     <t>A01, A12</t>
@@ -316,10 +316,10 @@
     <t>A15</t>
   </si>
   <si>
-    <t>Notifications temps réel (SSE) et écran transverse</t>
-  </si>
-  <si>
-    <t>core/notifications/notifications.store.ts (flux SSE partagé), écran /notifications, badge cloche</t>
+    <t>Notifications en temps réel</t>
+  </si>
+  <si>
+    <t>Alerte immédiate à l'écran, compteur de messages non lus et écran de consultation ouvert aux dix profils</t>
   </si>
   <si>
     <t>core/notifications/notification-route.ts et features/transverse/notifications-page.ts créés le 11/08 (« clic → écran d'action, mapping type × rôle ») ; notifications.store.ts créé le 15/08 au commit 9552c0c</t>
@@ -328,10 +328,10 @@
     <t>A16</t>
   </si>
   <si>
-    <t>Observations du PV, navette post-signature et table PPM commune</t>
-  </si>
-  <si>
-    <t>Cartes d'observation partagées, décisions du vérificateur, réexamen, formulaire de réception partagé</t>
+    <t>Observations du procès-verbal et navette après signature</t>
+  </si>
+  <si>
+    <t>Suivi de chaque observation jusqu'à sa levée, décisions du vérificateur, réexamen d'un dossier rectifié, formulaire de réception commun aux profils</t>
   </si>
   <si>
     <t>A02, A09</t>
@@ -343,10 +343,10 @@
     <t>A17</t>
   </si>
   <si>
-    <t>Audit technique : traitement des constats sécurité, accessibilité, performance</t>
-  </si>
-  <si>
-    <t>AUDIT.md — 35 constats, corrections livrées et vérifiées</t>
+    <t>Traitement des constats de l'audit technique</t>
+  </si>
+  <si>
+    <t>Correction des 35 constats de sécurité, d'accessibilité, de performance et de dépendances, chacun vérifié et tracé dans AUDIT.md</t>
   </si>
   <si>
     <t>en_retard</t>
@@ -358,10 +358,10 @@
     <t>A18</t>
   </si>
   <si>
-    <t>Session en cookie HttpOnly et passage en même origine</t>
-  </si>
-  <si>
-    <t>proxy /api, apiUrl relative, suppression de tout jeton côté client</t>
+    <t>Sécurisation de la session par cookie</t>
+  </si>
+  <si>
+    <t>Session portée par un cookie inaccessible au JavaScript, application et API servies sous la même origine, plus aucun jeton conservé dans le navigateur</t>
   </si>
   <si>
     <t>J3</t>
@@ -373,10 +373,10 @@
     <t>A19</t>
   </si>
   <si>
-    <t>Actualités à la connexion</t>
-  </si>
-  <si>
-    <t>Modal d'actualités + écran d'administration (front) et API /api/actualites (backend)</t>
+    <t>Actualités présentées à la connexion</t>
+  </si>
+  <si>
+    <t>Message d'information affiché à l'ouverture de session, écran d'administration pour le rédiger et le cibler par profil, et le service qui le délivre</t>
   </si>
   <si>
     <t>Front livré et recetté : 9faaa14 (19/08) « modal à la connexion + administration », shared/actualites/{actualites-modal,markdown,markdown-vue}.ts + markdown.spec.ts, services/actualite.services.ts, features/admin/actualites-admin.ts. API backend NON COMMITÉE : docs/demande-backend-2026-08-19.md §A liste 17 fichiers non suivis par git. Avancement = 1 des 2 moitiés (front livré / API versionnée).</t>
@@ -385,10 +385,10 @@
     <t>A20</t>
   </si>
   <si>
-    <t>Détail du plan de passation en onglets et UGPM rattachées</t>
-  </si>
-  <si>
-    <t>Modal de détail PPM à trois onglets, visibilité des unités de gestion pour les contrôleurs</t>
+    <t>Consultation du plan de passation en onglets</t>
+  </si>
+  <si>
+    <t>Fiche de dossier réorganisée en trois onglets, avec les unités de gestion rattachées enfin visibles par les contrôleurs</t>
   </si>
   <si>
     <t>A09, A14</t>
@@ -403,7 +403,7 @@
     <t>Tests automatisés et intégration continue</t>
   </si>
   <si>
-    <t>Suite unitaire, CI GitHub Actions, scénarios e2e versionnés</t>
+    <t>Suite de tests unitaires, exécution automatique à chaque livraison, scénarios de bout en bout versionnés dans le dépôt</t>
   </si>
   <si>
     <t>85 tests / 8 fichiers, 100 % au vert (`npx ng test --watch=false`, 2,97 s, exécuté le 26/08). Constats « Tests » de AUDIT.md : T2 clos (.github/workflows/ci.yml, commit b350579 du 17/08 — tests + build + npm audit bloquant), T1 entamé (0a4fe15 du 19/08, barrières anti-XSS couvertes), T3 ouvert (aucun e2e versionné, 0 fichier sous e2e/). Avancement = 1 constat clos sur 3.</t>
@@ -415,7 +415,7 @@
     <t>Polissage du module « Dossiers de planification »</t>
   </si>
   <si>
-    <t>Reprise de finition des écrans du module de planification avant reprise du développement</t>
+    <t>Reprise de finition des écrans de planification, avant que le développement ne redémarre</t>
   </si>
   <si>
     <t>en_cours</t>
@@ -430,10 +430,10 @@
     <t>A22</t>
   </si>
   <si>
-    <t>Gestion des délais légaux d'instruction</t>
-  </si>
-  <si>
-    <t>Calcul du délai réglementaire par dossier, alerte ALERTE_DELAI, indicateur de dépassement</t>
+    <t>Délais réglementaires d'instruction</t>
+  </si>
+  <si>
+    <t>Décompte du délai légal sur chaque dossier, alerte à l'approche de l'échéance et signalement des dépassements</t>
   </si>
   <si>
     <t>a_venir</t>
@@ -448,10 +448,10 @@
     <t>A23</t>
   </si>
   <si>
-    <t>Indicateurs de performance : écrans manquants</t>
-  </si>
-  <si>
-    <t>Écrans « Indicateurs contrôleurs » et « Indicateurs PRMP »</t>
+    <t>Indicateurs de performance des contrôleurs et des autorités de passation</t>
+  </si>
+  <si>
+    <t>Deux écrans de restitution : activité et conformité par contrôleur, puis par autorité de passation et par exercice budgétaire</t>
   </si>
   <si>
     <t>A07, A26</t>
@@ -463,10 +463,10 @@
     <t>A24</t>
   </si>
   <si>
-    <t>Journal d'audit : écran de recherche dédié</t>
-  </si>
-  <si>
-    <t>Écran de consultation filtrable du journal (acteur, dossier, période, action)</t>
+    <t>Consultation du journal d'audit</t>
+  </si>
+  <si>
+    <t>Écran de recherche du journal, filtrable par acteur, dossier, période et nature de l'action</t>
   </si>
   <si>
     <t>A01, A26</t>
@@ -478,10 +478,10 @@
     <t>A25</t>
   </si>
   <si>
-    <t>Recette du module 1 et livraison contractuelle</t>
-  </si>
-  <si>
-    <t>Procès-verbal de recette, mise en production du module 1</t>
+    <t>Recette et livraison du module 1</t>
+  </si>
+  <si>
+    <t>Procès-verbal de recette signé et mise en production du module de planification</t>
   </si>
   <si>
     <t>A17, A19, A21, A22, A23, A24</t>
@@ -562,19 +562,19 @@
     <t>Module 1 — Socle transversal et dossiers de planification</t>
   </si>
   <si>
-    <t>Authentification, habilitations, référentiels, workflow d'instruction, notifications, journal d'audit, tableaux de bord, contrôle des plans de passation</t>
-  </si>
-  <si>
-    <t>Inventaire des 14 fonctions du module 1 (constat du 26/08, chaque ligne adossée à un fichier) : 10 implémentées (auth, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications), 3 partielles (statistiques, journal d'audit, actualités), 1 absente (délais légaux). Avancement = (10×100 + 3×50 + 1×0) / 14 = 82 %.</t>
+    <t>Authentification, habilitations, référentiels, circuit d'instruction, délais réglementaires, notifications, journal d'audit et tableaux de bord — appliqués au contrôle des plans de passation</t>
+  </si>
+  <si>
+    <t>Inventaire des 14 fonctions du module 1 (constat du 26/08) : 10 implémentées (authentification, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications), 3 partielles (statistiques, journal d'audit, actualités), 1 absente (délais réglementaires). Avancement = (10×100 + 3×50 + 1×0) / 14 = 82 %. Le détail fonction par fonction est porté par les activités A01 à A26 de ce fichier, chacune avec sa propre preuve — commit, fichier du dépôt (src/app/…) ou exécution de test.</t>
   </si>
   <si>
     <t>G02</t>
   </si>
   <si>
-    <t>Recette, correction et mise en production du module 1</t>
-  </si>
-  <si>
-    <t>PV de recette, déploiement, reprise des réserves</t>
+    <t>Recette et mise en production du module 1</t>
+  </si>
+  <si>
+    <t>Procès-verbal de recette, déploiement en production et reprise des réserves</t>
   </si>
   <si>
     <t>Découpage PROPOSÉ — aucun calendrier contractuel au-delà des 3 mois n'est connu.</t>
@@ -583,10 +583,10 @@
     <t>G03</t>
   </si>
   <si>
-    <t>Module 2 — Dossiers de mise en concurrence (DMC)</t>
-  </si>
-  <si>
-    <t>Dossiers d'appel à concurrence, procédures dérogatoires, rapports d'évaluation</t>
+    <t>Module 2 — Dossiers de mise en concurrence</t>
+  </si>
+  <si>
+    <t>Contrôle des dossiers d'appel à concurrence, des procédures dérogatoires et des rapports d'évaluation</t>
   </si>
   <si>
     <t>J5</t>
@@ -598,7 +598,7 @@
     <t>G04</t>
   </si>
   <si>
-    <t>Module 3 — Dossiers de marchés (projets de marchés et avenants)</t>
+    <t>Module 3 — Dossiers de marchés</t>
   </si>
   <si>
     <t>Contrôle des projets de marchés et des avenants avant approbation</t>
@@ -616,7 +616,7 @@
     <t>Module 4 — Actes de gestion contractuelle</t>
   </si>
   <si>
-    <t>Contrôle des décisions d'octroi d'indemnité, sursis d'exécution, remise de pénalité, résiliation</t>
+    <t>Contrôle des décisions d'octroi d'indemnité, de sursis d'exécution, de remise de pénalité et de résiliation</t>
   </si>
   <si>
     <t>J7</t>
@@ -628,10 +628,10 @@
     <t>G06</t>
   </si>
   <si>
-    <t>Recette globale, reprise de données et déploiement PRS 2.0</t>
-  </si>
-  <si>
-    <t>Recette des 4 modules, mise en production</t>
+    <t>Recette générale et mise en production de PRS 2.0</t>
+  </si>
+  <si>
+    <t>Recette des quatre modules, reprise des données et déploiement en production</t>
   </si>
   <si>
     <t>G02, G03, G04, G05</t>

--- a/chronogrammes/chronogramme_prs2.xlsx
+++ b/chronogrammes/chronogramme_prs2.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="294">
   <si>
     <t>PRS 2.0 — Module 1 : socle transversal et dossiers de planification (Gantt hebdomadaire)</t>
   </si>
   <si>
-    <t>Arrêté au 26/08/2026 · 26 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
+    <t>Arrêté au 28/08/2026 · 26 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
   </si>
   <si>
     <t>ID</t>
@@ -352,7 +352,7 @@
     <t>en_retard</t>
   </si>
   <si>
-    <t>AUDIT.md §3 dénombre 35 constats (S1-S13, P1-P11, A1-A7, T1-T3, D1). Clos et vérifiés : 27 (dont 9ff24e9 directive appModale, f8dca39 112 routes en loadComponent, b350579 polices + CI, 1216458 contraste AA 114→17 textes, 1c4ab1c scope sur 225 en-têtes). Restent ouverts : P1, P9 (extension), A2b, S9, S12, P10, T1 (entamé), T3 = 8. Avancement = 27/35 = 77 %.</t>
+    <t>AUDIT.md §3 dénombre 35 constats (S1-S13, P1-P11, A1-A7, T1-T3, D1), auxquels s'ajoute C-1 issu du nouvel audit global du 27/08 — soit 36. Clos et vérifiés : 30. Chantiers du 27/08 (AUDIT.md, deux entrées) : les 124 avertissements ESLint d'accessibilité soldés (6523668 → 1d097e5, 8 commits, 34 fichiers — le clic sur le voile passe dans la directive appModale) ; P1 ENFIN ADOPTÉ (238293b → b103221, 20 commits : recherche de la topbar résolue côté serveur, « Mes dossiers » et pipeline paginés, rendu incrémental des trois files sans endpoint paginé) ; P9 étendu ; C-1 clos le jour même. Restent ouverts : A2b, S9, S12, P10, T1 (entamé), T3 = 6. Avancement = 30/36 = 83 % (était 27/35 = 77 % au 26/08).</t>
   </si>
   <si>
     <t>A18</t>
@@ -379,7 +379,7 @@
     <t>Message d'information affiché à l'ouverture de session, écran d'administration pour le rédiger et le cibler par profil, et le service qui le délivre</t>
   </si>
   <si>
-    <t>Front livré et recetté : 9faaa14 (19/08) « modal à la connexion + administration », shared/actualites/{actualites-modal,markdown,markdown-vue}.ts + markdown.spec.ts, services/actualite.services.ts, features/admin/actualites-admin.ts. API backend NON COMMITÉE : docs/demande-backend-2026-08-19.md §A liste 17 fichiers non suivis par git. Avancement = 1 des 2 moitiés (front livré / API versionnée).</t>
+    <t>Front : commit 9faaa14 (19/08) « modal à la connexion + administration » — shared/actualites/{actualites-modal,markdown,markdown-vue}.ts + markdown.spec.ts, services/actualite.services.ts, features/admin/actualites-admin.ts. API : commit backend 51620f4 du 19/08 également (dépôt PRS20) — ActualiteController, ActualiteDto, entités Actualite / ActualiteImage / ActualiteProfil, enum StatutActualite, tous suivis par git. CORRECTION DU 28/08 : l'activité était portée à 50 % au motif que l'API n'était pas versionnée. C'était exact au moment où docs/demande-backend-2026-08-19.md a été écrit, en cours de journée, mais le backend a commité le soir même — le document décrivait une situation en vol, pas un état final. Leçon : vérifier le dépôt concerné, pas la demande qui lui a été adressée.</t>
   </si>
   <si>
     <t>A20</t>
@@ -406,7 +406,7 @@
     <t>Suite de tests unitaires, exécution automatique à chaque livraison, scénarios de bout en bout versionnés dans le dépôt</t>
   </si>
   <si>
-    <t>85 tests / 8 fichiers, 100 % au vert (`npx ng test --watch=false`, 2,97 s, exécuté le 26/08). Constats « Tests » de AUDIT.md : T2 clos (.github/workflows/ci.yml, commit b350579 du 17/08 — tests + build + npm audit bloquant), T1 entamé (0a4fe15 du 19/08, barrières anti-XSS couvertes), T3 ouvert (aucun e2e versionné, 0 fichier sous e2e/). Avancement = 1 constat clos sur 3.</t>
+    <t>106 tests / 12 fichiers, 100 % au vert (`npx ng test --watch=false`, exécuté le 28/08 — était 85 / 8 au 26/08). Progression tracée dans AUDIT.md : 42 → 83 (19/08) → 93 (a11y du 27/08, directive de modale couverte) → 106 (contrat de la recherche serveur et de la pagination, 238293b). La CI exécute désormais aussi ESLint 9 (.github/workflows/ci.yml). Constats « Tests » : T2 clos (CI, b350579 du 17/08), T1 toujours ENTAMÉ (la couverture progresse mais n'est ni mesurée ni au niveau visé), T3 OUVERT (aucun scénario e2e versionné). Avancement = 1 constat clos sur 3 — inchangé malgré la croissance des tests : c'est la couverture mesurée et les e2e qui manquent, pas le nombre de cas.</t>
   </si>
   <si>
     <t>A26</t>
@@ -424,7 +424,7 @@
     <t>A09, A16, A20</t>
   </si>
   <si>
-    <t>Avancement = 3 jours ouvrés écoulés sur 5 au 26/08 — RATIO DE TEMPS, non une mesure de travail accompli : arbitrage du pilote faute de mesure disponible. ⚠️ Non observable dans le dépôt : dernier commit `bec0e39` du 20/08, aucun commit depuis. Le polissage des 24, 25 et 26/08 n'est pas versionné — à commiter avant toute relance de la mesure (cf. AUDIT.md, constat S11 sur les livraisons non suivies).</t>
+    <t>RÉSERVE LEVÉE LE 28/08 — le travail est versionné. Le chronogramme du 26/08 notait « aucun commit depuis bec0e39 du 20/08 » ; il y en a eu 39 depuis, dont 32 le 27/08. Pour la part planification : sortie des sous-dialogues du détail PPM (7dfc4d8, bf991eb, 2faf937, f5cf8ec), pagination serveur de « Mes dossiers » (2f51efa), voiles de modales rendus au décor (9bcf8e3). Avancement = 4 jours ouvrés révolus sur 5 au matin du 28/08 — RATIO DE TEMPS, non une mesure de travail accompli.</t>
   </si>
   <si>
     <t>A22</t>
@@ -469,10 +469,7 @@
     <t>Écran de recherche du journal, filtrable par acteur, dossier, période et nature de l'action</t>
   </si>
   <si>
-    <t>A01, A26</t>
-  </si>
-  <si>
-    <t>Existant : écran CRUD générique en lecture seule /admin/audit (admin.routes.ts:86, admin-resources.config.ts:571-577) et journal métier par dossier (services/circuit.services.ts:58). Manque un écran de recherche transverse.</t>
+    <t>Livré le 27/08, en avance sur la date proposée (31/08) et sans attendre la fin du polissage : commit ad40144 « le journal d'audit se lit page par page, filtré par table, acteur et période ». Écran dédié features/admin/audit-logs-admin.ts, routé en admin.routes.ts:87 — il remplace le CRUD générique qui demandait la table entière (constat C-1 du nouvel audit du 27/08). État d'erreur avec reprise branché au passage (constat P9). AUDIT.md, entrée du 27/08.</t>
   </si>
   <si>
     <t>A25</t>
@@ -493,7 +490,7 @@
     <t>Démarre au lendemain de A22 (goulot, fin le 11/09) et conserve ses 5 jours ouvrés grâce au décalage d'échéance décidé le 26/08 : 14/09 → 18/09. Dates PROPOSÉES.</t>
   </si>
   <si>
-    <t>▲ 26/08/2026</t>
+    <t>▲ 28/08/2026</t>
   </si>
   <si>
     <t>▲</t>
@@ -523,7 +520,7 @@
     <t>PRS 2.0 — Vue globale des 4 modules (Gantt mensuel)</t>
   </si>
   <si>
-    <t>Arrêté au 26/08/2026 · 6 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
+    <t>Arrêté au 28/08/2026 · 6 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
   </si>
   <si>
     <t>M1</t>
@@ -565,7 +562,7 @@
     <t>Authentification, habilitations, référentiels, circuit d'instruction, délais réglementaires, notifications, journal d'audit et tableaux de bord — appliqués au contrôle des plans de passation</t>
   </si>
   <si>
-    <t>Inventaire des 14 fonctions du module 1 (constat du 26/08) : 10 implémentées (authentification, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications), 3 partielles (statistiques, journal d'audit, actualités), 1 absente (délais réglementaires). Avancement = (10×100 + 3×50 + 1×0) / 14 = 82 %. Le détail fonction par fonction est porté par les activités A01 à A26 de ce fichier, chacune avec sa propre preuve — commit, fichier du dépôt (src/app/…) ou exécution de test.</t>
+    <t>Inventaire des 14 fonctions du module 1, réexaminé le 28/08 : 12 implémentées (authentification, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications, journal d'audit, actualités), 1 partielle (statistiques — les écrans d'indicateurs par contrôleur et par autorité de passation manquent, cf. A23), 1 absente (délais réglementaires, cf. A22). Avancement = (12×100 + 1×50 + 1×0) / 14 = 89 %. Deux fonctions ont changé de statut depuis le 26/08 : le journal d'audit passe de partielle à implémentée (écran dédié livré le 27/08, A24) et les actualités de partielle à implémentée (l'API backend était en réalité commitée dès le 19/08, A19). Le détail fonction par fonction est porté par les activités A01 à A26 de ce fichier, chacune avec sa propre preuve — commit, fichier du dépôt (src/app/…) ou exécution de test.</t>
   </si>
   <si>
     <t>G02</t>
@@ -809,13 +806,13 @@
     <t>Activités module 1</t>
   </si>
   <si>
-    <t>18 terminées · 1 en cours · 4 à venir</t>
+    <t>20 terminées · 1 en cours · 3 à venir</t>
   </si>
   <si>
     <t>Avancement pondéré (durées)</t>
   </si>
   <si>
-    <t>78 %</t>
+    <t>81 %</t>
   </si>
   <si>
     <t>Σ(avancement × durée) / Σ(durée) sur le module 1.</t>
@@ -824,7 +821,7 @@
     <t>Avancement module 1 déclaré</t>
   </si>
   <si>
-    <t>82 %</t>
+    <t>89 %</t>
   </si>
   <si>
     <t>Valeur portée par la ligne globale, adossée à sa preuve.</t>
@@ -833,7 +830,7 @@
     <t>Activités en retard</t>
   </si>
   <si>
-    <t>A17, A19, A21</t>
+    <t>A17, A21</t>
   </si>
   <si>
     <t>Jalons franchis</t>
@@ -848,7 +845,7 @@
     <t>18/09/2026</t>
   </si>
   <si>
-    <t>J4 — Recette du module 1 — livraison contractuelle (dans 23 jours)</t>
+    <t>J4 — Recette du module 1 — livraison contractuelle (dans 21 jours)</t>
   </si>
   <si>
     <t>Chemin critique — module 1</t>
@@ -869,7 +866,7 @@
     <t>5 lignes.</t>
   </si>
   <si>
-    <t>AVERTISSEMENTS (15)</t>
+    <t>AVERTISSEMENTS (14)</t>
   </si>
   <si>
     <t>• A06 : début déclaré le 26/06/2026 (jour non ouvré) → décalé au 29/06/2026.</t>
@@ -908,10 +905,7 @@
     <t>• A12 : démarre le 27/07/2026, avant la fin de sa dépendance A11 (27/07/2026) — chevauchement assumé, non replanifié.</t>
   </si>
   <si>
-    <t>• A17 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 77 %).</t>
-  </si>
-  <si>
-    <t>• A19 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 50 %).</t>
+    <t>• A17 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 83 %).</t>
   </si>
   <si>
     <t>• A21 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 33 %).</t>
@@ -1120,7 +1114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1176,6 +1170,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2533,7 +2528,7 @@
         <v>111</v>
       </c>
       <c r="F21" s="11">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="G21" s="12">
         <f>Parametres!$B$2+61</f>
@@ -2623,11 +2618,11 @@
       <c r="D23" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>111</v>
+      <c r="E23" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="F23" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="12">
         <f>Parametres!$B$2+63</f>
@@ -2652,7 +2647,7 @@
       <c r="M23" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="W23" s="17"/>
+      <c r="W23" s="13"/>
       <c r="X23" s="14"/>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -2763,7 +2758,7 @@
         <v>134</v>
       </c>
       <c r="F26" s="11">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G26" s="12">
         <f>Parametres!$B$2+68</f>
@@ -2895,47 +2890,46 @@
       <c r="D29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>140</v>
+      <c r="E29" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="F29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="12">
-        <f>Parametres!$B$2+75</f>
-        <v>46265</v>
+        <f>Parametres!$B$2+71</f>
+        <v>46261</v>
       </c>
       <c r="H29" s="12">
-        <f>Parametres!$B$2+77</f>
-        <v>46267</v>
+        <f>Parametres!$B$2+71</f>
+        <v>46261</v>
       </c>
       <c r="I29" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M29" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="24"/>
+      <c r="X29" s="25"/>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="C30" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>92</v>
@@ -2958,68 +2952,68 @@
         <v>5</v>
       </c>
       <c r="J30" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X30" s="14"/>
       <c r="Z30" s="24"/>
-      <c r="AA30" s="25" t="s">
+      <c r="AA30" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="X31" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="X31" s="27" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
-      <c r="B34" s="29" t="s">
-        <v>162</v>
+      <c r="B34" s="30" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="20"/>
-      <c r="B35" s="29" t="s">
-        <v>163</v>
+      <c r="B35" s="30" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
-      <c r="B36" s="29" t="s">
-        <v>164</v>
+      <c r="B36" s="30" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="29" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="30" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="29" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3057,7 +3051,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3084,7 +3078,7 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3150,34 +3144,34 @@
         <v>14</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -3227,13 +3221,13 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>182</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>92</v>
@@ -3242,7 +3236,7 @@
         <v>134</v>
       </c>
       <c r="F5" s="11">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="G5" s="12">
         <f>Parametres!$B$2+0</f>
@@ -3259,30 +3253,30 @@
         <v>35</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="21"/>
-      <c r="Q5" s="30" t="s">
+      <c r="Q5" s="31" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>186</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>92</v>
@@ -3305,7 +3299,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>35</v>
@@ -3314,20 +3308,20 @@
         <v>35</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P6" s="14"/>
       <c r="Q6" s="24"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>92</v>
@@ -3350,33 +3344,33 @@
         <v>45</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P7" s="14"/>
       <c r="Q7" s="24"/>
       <c r="R7" s="24"/>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>92</v>
@@ -3399,33 +3393,33 @@
         <v>45</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P8" s="14"/>
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
-      <c r="U8" s="25" t="s">
+      <c r="U8" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>92</v>
@@ -3448,32 +3442,32 @@
         <v>35</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P9" s="14"/>
       <c r="U9" s="24"/>
-      <c r="V9" s="25" t="s">
+      <c r="V9" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>92</v>
@@ -3496,68 +3490,68 @@
         <v>25</v>
       </c>
       <c r="J10" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P10" s="14"/>
       <c r="V10" s="24"/>
-      <c r="W10" s="25" t="s">
+      <c r="W10" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="P11" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="P11" s="27" t="s">
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
-      <c r="B14" s="29" t="s">
-        <v>162</v>
+      <c r="B14" s="30" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
-      <c r="B15" s="29" t="s">
-        <v>163</v>
+      <c r="B15" s="30" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
-      <c r="B16" s="29" t="s">
-        <v>164</v>
+      <c r="B16" s="30" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="30" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="29" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3589,7 +3583,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3599,95 +3593,95 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="B4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <f>Parametres!$B$2+8</f>
         <v>46198</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F4" s="8" t="s">
+    </row>
+    <row r="5" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="5" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <f>Parametres!$B$2+40</f>
         <v>46230</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F5" s="8" t="s">
+    </row>
+    <row r="6" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="6" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>Parametres!$B$2+63</f>
         <v>46253</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="8" t="s">
+    </row>
+    <row r="7" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="7" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="B7" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>Parametres!$B$2+93</f>
         <v>46283</v>
       </c>
@@ -3695,20 +3689,20 @@
         <v>140</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="B8" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>Parametres!$B$2+156</f>
         <v>46346</v>
       </c>
@@ -3716,20 +3710,20 @@
         <v>140</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="B9" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>Parametres!$B$2+219</f>
         <v>46409</v>
       </c>
@@ -3737,20 +3731,20 @@
         <v>140</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>Parametres!$B$2+268</f>
         <v>46458</v>
       </c>
@@ -3758,20 +3752,20 @@
         <v>140</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>Parametres!$B$2+303</f>
         <v>46493</v>
       </c>
@@ -3779,7 +3773,7 @@
         <v>140</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>35</v>
@@ -3796,7 +3790,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3806,303 +3800,296 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="35">
+        <v>46190</v>
+      </c>
+      <c r="C2" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="34">
-        <v>46190</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="B3" s="37">
+        <v>46262</v>
+      </c>
+      <c r="C3" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="36">
-        <v>46260</v>
-      </c>
-      <c r="C3" s="37" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="B4" s="37">
+        <v>46283</v>
+      </c>
+      <c r="C4" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="B4" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C4" s="37" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="37" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="C6" s="37" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="B7" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="B9" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="B10" s="36">
+        <v>26</v>
+      </c>
+      <c r="C10" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="35">
-        <v>26</v>
-      </c>
-      <c r="C10" s="37" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="B11" s="36" t="s">
         <v>261</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="C11" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="C11" s="37" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="37" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+      <c r="B13" s="36">
+        <v>2</v>
+      </c>
+      <c r="C13" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="B13" s="35">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="36">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="B14" s="35">
-        <v>3</v>
-      </c>
-      <c r="C14" s="37" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="B15" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="C15" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="C15" s="37" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="B16" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="C16" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="C16" s="37" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="B17" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="C17" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="C17" s="37" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="41" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="41" t="s">
         <v>291</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="41" t="s">
         <v>292</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -4117,7 +4104,6 @@
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/chronogrammes/chronogramme_prs2.xlsx
+++ b/chronogrammes/chronogramme_prs2.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="300">
   <si>
     <t>PRS 2.0 — Module 1 : socle transversal et dossiers de planification (Gantt hebdomadaire)</t>
   </si>
   <si>
-    <t>Arrêté au 28/08/2026 · 26 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
+    <t>Arrêté au 01/09/2026 · 27 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
   </si>
   <si>
     <t>ID</t>
@@ -352,7 +352,7 @@
     <t>en_retard</t>
   </si>
   <si>
-    <t>AUDIT.md §3 dénombre 35 constats (S1-S13, P1-P11, A1-A7, T1-T3, D1), auxquels s'ajoute C-1 issu du nouvel audit global du 27/08 — soit 36. Clos et vérifiés : 30. Chantiers du 27/08 (AUDIT.md, deux entrées) : les 124 avertissements ESLint d'accessibilité soldés (6523668 → 1d097e5, 8 commits, 34 fichiers — le clic sur le voile passe dans la directive appModale) ; P1 ENFIN ADOPTÉ (238293b → b103221, 20 commits : recherche de la topbar résolue côté serveur, « Mes dossiers » et pipeline paginés, rendu incrémental des trois files sans endpoint paginé) ; P9 étendu ; C-1 clos le jour même. Restent ouverts : A2b, S9, S12, P10, T1 (entamé), T3 = 6. Avancement = 30/36 = 83 % (était 27/35 = 77 % au 26/08).</t>
+    <t>AUDIT.md §3 dénombre 35 constats (S1-S13, P1-P11, A1-A7, T1-T3, D1), auxquels s'ajoute C-1 issu du nouvel audit global du 27/08 — soit 36. Clos et vérifiés : 31. Chantiers du 27/08 (AUDIT.md, deux entrées) : les 124 avertissements ESLint d'accessibilité soldés (6523668 → 1d097e5, 8 commits, 34 fichiers — le clic sur le voile passe dans la directive appModale) ; P1 ENFIN ADOPTÉ (238293b → b103221, 20 commits : recherche de la topbar résolue côté serveur, « Mes dossiers » et pipeline paginés, rendu incrémental des trois files sans endpoint paginé) ; P9 étendu ; C-1 clos le jour même. S9 CLOS le 31/08 (ffd84a8) : rendu sans objet par le retrait des interrupteurs de délégation (23d7e7f, 28/08) — la clé n'est plus écrite, purge au logout, cinq mentions annotées dans AUDIT.md. Restent ouverts : A2b, S12, P10, T1 (entamé), T3 = 5. Avancement = 31/36 = 86 % (était 30/36 = 83 % au 28/08).</t>
   </si>
   <si>
     <t>A18</t>
@@ -406,7 +406,7 @@
     <t>Suite de tests unitaires, exécution automatique à chaque livraison, scénarios de bout en bout versionnés dans le dépôt</t>
   </si>
   <si>
-    <t>106 tests / 12 fichiers, 100 % au vert (`npx ng test --watch=false`, exécuté le 28/08 — était 85 / 8 au 26/08). Progression tracée dans AUDIT.md : 42 → 83 (19/08) → 93 (a11y du 27/08, directive de modale couverte) → 106 (contrat de la recherche serveur et de la pagination, 238293b). La CI exécute désormais aussi ESLint 9 (.github/workflows/ci.yml). Constats « Tests » : T2 clos (CI, b350579 du 17/08), T1 toujours ENTAMÉ (la couverture progresse mais n'est ni mesurée ni au niveau visé), T3 OUVERT (aucun scénario e2e versionné). Avancement = 1 constat clos sur 3 — inchangé malgré la croissance des tests : c'est la couverture mesurée et les e2e qui manquent, pas le nombre de cas.</t>
+    <t>136 tests / 15 fichiers, 100 % au vert (`npx ng test --watch=false`, exécuté le 01/09 — était 106 / 12 au 28/08). Progression tracée dans AUDIT.md : 42 → 83 (19/08) → 93 (a11y du 27/08) → 106 (recherche serveur et pagination, 238293b) → 136 (visa unique : peutViser et la machine d'états couverts, 9e2f2cf). La CI exécute aussi ESLint 9 (.github/workflows/ci.yml). Constats « Tests » : T2 clos (CI, b350579 du 17/08), T1 toujours ENTAMÉ (couverture ni mesurée ni au niveau visé), T3 toujours OUVERT — les recettes Playwright du 01/09 (visa, intérim, chaînes de contrôle : 22/22, 31/31, 16/16) ont tourné depuis le répertoire de session, AUCUN scénario n'est versionné dans le dépôt. Avancement = 1 constat clos sur 3.</t>
   </si>
   <si>
     <t>A26</t>
@@ -418,151 +418,166 @@
     <t>Reprise de finition des écrans de planification, avant que le développement ne redémarre</t>
   </si>
   <si>
+    <t>A09, A16, A20</t>
+  </si>
+  <si>
+    <t>Fenêtre du 24 au 28/08 révolue à l'arrêté du 01/09, développement repris (7c89f00 le 28/08 au soir — A27). Travail versionné : sortie des sous-dialogues du détail PPM (7dfc4d8, bf991eb, 2faf937, f5cf8ec), pagination serveur de « Mes dossiers » (2f51efa), voiles de modales rendus au décor (9bcf8e3), 39 commits entre le 20 et le 28/08.</t>
+  </si>
+  <si>
+    <t>A27</t>
+  </si>
+  <si>
+    <t>Visa du procès-verbal et chaînes de contrôle nominatives</t>
+  </si>
+  <si>
+    <t>Avis émis par le Membre dès l'examen, clôture de la navette en un seul visa réservé au dispatcheur, suppléance par intérim justifiée par une note, et rattachements Membre → Vérificateur → Assistant ciblant la vérification et l'archivage</t>
+  </si>
+  <si>
+    <t>A14, A16</t>
+  </si>
+  <si>
+    <t>Front : 7c89f00+0117b57 (co-signataire désigné, 28-30/08), 9e2f2cf (visa unique — avis du Membre à la soumission, visa du dispatcheur), e24c767 (visa par intérim, note PDF), 1934f6d+3eac6d8 (chaînes de contrôle : écran Admin/P/CC, files ciblées) — le backend PRS20 a livré en miroir jusqu'à f7cfe66. Recettes RÉELLES du 01/09 : PV#8 (visa normal) et PV#9 (visa par intérim) signés de bout en bout, chaînes posées à l'écran (16/16) ; e2e Playwright par interception 22/22 puis 31/31 ; en prime, cause racine CSRF (rotation du jeton × rafales) prouvée côté front et corrigée côté serveur, contre-recettée 4/4.</t>
+  </si>
+  <si>
+    <t>A22</t>
+  </si>
+  <si>
+    <t>Délais réglementaires d'instruction</t>
+  </si>
+  <si>
+    <t>Décompte du délai légal sur chaque dossier, alerte à l'approche de l'échéance et signalement des dépassements</t>
+  </si>
+  <si>
+    <t>a_venir</t>
+  </si>
+  <si>
+    <t>A02, A26, A27</t>
+  </si>
+  <si>
+    <t>Absent du code : 0 occurrence de `ALERTE_DELAI` dans src/ alors que docs/regles-gestion.md:370 et :485 la spécifient. Le seul dispositif temporel livré est features/prmp/calendrier-marches.ts — jalons CAPM du plan de l'autorité contractante (imminent / en retard), et non le délai d'instruction du contrôleur. Trois indicateurs déjà modélisés en dépendent : delaiMoyenExamen, delaiMoyenJours, delaiMoyCorrectionJours (models/pilotage.model.ts:85,101,116).</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>Indicateurs de performance des contrôleurs et des autorités de passation</t>
+  </si>
+  <si>
+    <t>Deux écrans de restitution : activité et conformité par contrôleur, puis par autorité de passation et par exercice budgétaire</t>
+  </si>
+  <si>
+    <t>A07, A26, A27</t>
+  </si>
+  <si>
+    <t>IndicateurCtrl et IndicateurPrmp sont modélisés (models/pilotage.model.ts:76-116) et servis (services/pilotage.services.ts) mais aucun écran ne les affiche. SNAPSHOT_STATS_CONFIG n'est plus référencé par aucune route (pilotage-resources.config.ts:6-11). Livrés par A07 : 3 écrans sur les 5 dénombrés.</t>
+  </si>
+  <si>
+    <t>A24</t>
+  </si>
+  <si>
+    <t>Consultation du journal d'audit</t>
+  </si>
+  <si>
+    <t>Écran de recherche du journal, filtrable par acteur, dossier, période et nature de l'action</t>
+  </si>
+  <si>
+    <t>Livré le 27/08, en avance sur la date proposée (31/08) et sans attendre la fin du polissage : commit ad40144 « le journal d'audit se lit page par page, filtré par table, acteur et période ». Écran dédié features/admin/audit-logs-admin.ts, routé en admin.routes.ts:87 — il remplace le CRUD générique qui demandait la table entière (constat C-1 du nouvel audit du 27/08). État d'erreur avec reprise branché au passage (constat P9). AUDIT.md, entrée du 27/08.</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>Recette et livraison du module 1</t>
+  </si>
+  <si>
+    <t>Procès-verbal de recette signé et mise en production du module de planification</t>
+  </si>
+  <si>
+    <t>A17, A19, A21, A22, A23, A24</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Dates du 26/08 CONSERVÉES (14 → 18/09) mais désormais EN CONFLIT avec A22 décalée (fin 15/09) : le générateur le signale. Voir la note de A22 — l'arbitrage (compression, chevauchement ou décalage d'échéance) appartient au pilote. Dates PROPOSÉES.</t>
+  </si>
+  <si>
+    <t>▲ 01/09/2026</t>
+  </si>
+  <si>
+    <t>▲</t>
+  </si>
+  <si>
+    <t>Légende</t>
+  </si>
+  <si>
+    <t>Terminé</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>À venir</t>
+  </si>
+  <si>
+    <t>En retard</t>
+  </si>
+  <si>
+    <t>◆ jalon      ▲ / trait orange : date d’arrêté (« aujourd’hui »)</t>
+  </si>
+  <si>
+    <t>◆ en colonne « Critique » : activité du chemin critique</t>
+  </si>
+  <si>
+    <t>PRS 2.0 — Vue globale des 4 modules (Gantt mensuel)</t>
+  </si>
+  <si>
+    <t>Arrêté au 01/09/2026 · 6 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>Module 1 — Socle transversal et dossiers de planification</t>
+  </si>
+  <si>
+    <t>Authentification, habilitations, référentiels, circuit d'instruction, délais réglementaires, notifications, journal d'audit et tableaux de bord — appliqués au contrôle des plans de passation</t>
+  </si>
+  <si>
     <t>en_cours</t>
   </si>
   <si>
-    <t>A09, A16, A20</t>
-  </si>
-  <si>
-    <t>RÉSERVE LEVÉE LE 28/08 — le travail est versionné. Le chronogramme du 26/08 notait « aucun commit depuis bec0e39 du 20/08 » ; il y en a eu 39 depuis, dont 32 le 27/08. Pour la part planification : sortie des sous-dialogues du détail PPM (7dfc4d8, bf991eb, 2faf937, f5cf8ec), pagination serveur de « Mes dossiers » (2f51efa), voiles de modales rendus au décor (9bcf8e3). Avancement = 4 jours ouvrés révolus sur 5 au matin du 28/08 — RATIO DE TEMPS, non une mesure de travail accompli.</t>
-  </si>
-  <si>
-    <t>A22</t>
-  </si>
-  <si>
-    <t>Délais réglementaires d'instruction</t>
-  </si>
-  <si>
-    <t>Décompte du délai légal sur chaque dossier, alerte à l'approche de l'échéance et signalement des dépassements</t>
-  </si>
-  <si>
-    <t>a_venir</t>
-  </si>
-  <si>
-    <t>A02, A26</t>
-  </si>
-  <si>
-    <t>Absent du code : 0 occurrence de `ALERTE_DELAI` dans src/ alors que docs/regles-gestion.md:370 et :485 la spécifient. Le seul dispositif temporel livré est features/prmp/calendrier-marches.ts — jalons CAPM du plan de l'autorité contractante (imminent / en retard), et non le délai d'instruction du contrôleur. Trois indicateurs déjà modélisés en dépendent : delaiMoyenExamen, delaiMoyenJours, delaiMoyCorrectionJours (models/pilotage.model.ts:85,101,116).</t>
-  </si>
-  <si>
-    <t>A23</t>
-  </si>
-  <si>
-    <t>Indicateurs de performance des contrôleurs et des autorités de passation</t>
-  </si>
-  <si>
-    <t>Deux écrans de restitution : activité et conformité par contrôleur, puis par autorité de passation et par exercice budgétaire</t>
-  </si>
-  <si>
-    <t>A07, A26</t>
-  </si>
-  <si>
-    <t>IndicateurCtrl et IndicateurPrmp sont modélisés (models/pilotage.model.ts:76-116) et servis (services/pilotage.services.ts) mais aucun écran ne les affiche. SNAPSHOT_STATS_CONFIG n'est plus référencé par aucune route (pilotage-resources.config.ts:6-11). Livrés par A07 : 3 écrans sur les 5 dénombrés.</t>
-  </si>
-  <si>
-    <t>A24</t>
-  </si>
-  <si>
-    <t>Consultation du journal d'audit</t>
-  </si>
-  <si>
-    <t>Écran de recherche du journal, filtrable par acteur, dossier, période et nature de l'action</t>
-  </si>
-  <si>
-    <t>Livré le 27/08, en avance sur la date proposée (31/08) et sans attendre la fin du polissage : commit ad40144 « le journal d'audit se lit page par page, filtré par table, acteur et période ». Écran dédié features/admin/audit-logs-admin.ts, routé en admin.routes.ts:87 — il remplace le CRUD générique qui demandait la table entière (constat C-1 du nouvel audit du 27/08). État d'erreur avec reprise branché au passage (constat P9). AUDIT.md, entrée du 27/08.</t>
-  </si>
-  <si>
-    <t>A25</t>
-  </si>
-  <si>
-    <t>Recette et livraison du module 1</t>
-  </si>
-  <si>
-    <t>Procès-verbal de recette signé et mise en production du module de planification</t>
-  </si>
-  <si>
-    <t>A17, A19, A21, A22, A23, A24</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>Démarre au lendemain de A22 (goulot, fin le 11/09) et conserve ses 5 jours ouvrés grâce au décalage d'échéance décidé le 26/08 : 14/09 → 18/09. Dates PROPOSÉES.</t>
-  </si>
-  <si>
-    <t>▲ 28/08/2026</t>
-  </si>
-  <si>
-    <t>▲</t>
-  </si>
-  <si>
-    <t>Légende</t>
-  </si>
-  <si>
-    <t>Terminé</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>À venir</t>
-  </si>
-  <si>
-    <t>En retard</t>
-  </si>
-  <si>
-    <t>◆ jalon      ▲ / trait orange : date d’arrêté (« aujourd’hui »)</t>
-  </si>
-  <si>
-    <t>◆ en colonne « Critique » : activité du chemin critique</t>
-  </si>
-  <si>
-    <t>PRS 2.0 — Vue globale des 4 modules (Gantt mensuel)</t>
-  </si>
-  <si>
-    <t>Arrêté au 28/08/2026 · 6 lignes · démarrage 17/06/2026 · échéance 18/09/2026</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>M5</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>M7</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>G01</t>
-  </si>
-  <si>
-    <t>Module 1 — Socle transversal et dossiers de planification</t>
-  </si>
-  <si>
-    <t>Authentification, habilitations, référentiels, circuit d'instruction, délais réglementaires, notifications, journal d'audit et tableaux de bord — appliqués au contrôle des plans de passation</t>
-  </si>
-  <si>
-    <t>Inventaire des 14 fonctions du module 1, réexaminé le 28/08 : 12 implémentées (authentification, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications, journal d'audit, actualités), 1 partielle (statistiques — les écrans d'indicateurs par contrôleur et par autorité de passation manquent, cf. A23), 1 absente (délais réglementaires, cf. A22). Avancement = (12×100 + 1×50 + 1×0) / 14 = 89 %. Deux fonctions ont changé de statut depuis le 26/08 : le journal d'audit passe de partielle à implémentée (écran dédié livré le 27/08, A24) et les actualités de partielle à implémentée (l'API backend était en réalité commitée dès le 19/08, A19). Le détail fonction par fonction est porté par les activités A01 à A26 de ce fichier, chacune avec sa propre preuve — commit, fichier du dépôt (src/app/…) ou exécution de test.</t>
+    <t>Inventaire des 14 fonctions du module 1, réexaminé le 28/08 : 12 implémentées (authentification, habilitations, référentiels, dépôt, complétude, affectation, instruction, visa, navette, notifications, journal d'audit, actualités), 1 partielle (statistiques — les écrans d'indicateurs par contrôleur et par autorité de passation manquent, cf. A23), 1 absente (délais réglementaires, cf. A22). Avancement = (12×100 + 1×50 + 1×0) / 14 = 89 %. Deux fonctions ont changé de statut depuis le 26/08 : le journal d'audit passe de partielle à implémentée (écran dédié livré le 27/08, A24) et les actualités de partielle à implémentée (l'API backend était en réalité commitée dès le 19/08, A19). Réexaminé le 01/09 : INCHANGÉ à 89 % — le chantier A27 (visa, intérim, chaînes de contrôle) approfondit des fonctions déjà comptées implémentées (visa, navette, habilitations) sans faire bouger les deux manquantes (délais, statistiques). Le détail fonction par fonction est porté par les activités A01 à A27 de ce fichier, chacune avec sa propre preuve — commit, fichier du dépôt (src/app/…) ou exécution de test.</t>
   </si>
   <si>
     <t>G02</t>
@@ -806,13 +821,13 @@
     <t>Activités module 1</t>
   </si>
   <si>
-    <t>20 terminées · 1 en cours · 3 à venir</t>
+    <t>22 terminées · 0 en cours · 3 à venir</t>
   </si>
   <si>
     <t>Avancement pondéré (durées)</t>
   </si>
   <si>
-    <t>81 %</t>
+    <t>83 %</t>
   </si>
   <si>
     <t>Σ(avancement × durée) / Σ(durée) sur le module 1.</t>
@@ -845,7 +860,7 @@
     <t>18/09/2026</t>
   </si>
   <si>
-    <t>J4 — Recette du module 1 — livraison contractuelle (dans 21 jours)</t>
+    <t>J4 — Recette du module 1 — livraison contractuelle (dans 17 jours)</t>
   </si>
   <si>
     <t>Chemin critique — module 1</t>
@@ -866,7 +881,7 @@
     <t>5 lignes.</t>
   </si>
   <si>
-    <t>AVERTISSEMENTS (14)</t>
+    <t>AVERTISSEMENTS (15)</t>
   </si>
   <si>
     <t>• A06 : début déclaré le 26/06/2026 (jour non ouvré) → décalé au 29/06/2026.</t>
@@ -905,10 +920,13 @@
     <t>• A12 : démarre le 27/07/2026, avant la fin de sa dépendance A11 (27/07/2026) — chevauchement assumé, non replanifié.</t>
   </si>
   <si>
-    <t>• A17 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 83 %).</t>
+    <t>• A17 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 86 %).</t>
   </si>
   <si>
     <t>• A21 : statut déclaré « en_cours », calculé « en_retard » (fin 19/08/2026, avancement 33 %).</t>
+  </si>
+  <si>
+    <t>• A25 : démarre le 14/09/2026, avant la fin de sa dépendance A22 (15/09/2026) — chevauchement assumé, non replanifié.</t>
   </si>
 </sst>
 </file>
@@ -977,11 +995,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF2563EB"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF9CA3AF"/>
       <sz val="9"/>
     </font>
@@ -992,6 +1005,11 @@
     <font>
       <b/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2563EB"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -1050,12 +1068,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
+        <fgColor rgb="FF9CA3AF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9CA3AF"/>
+        <fgColor rgb="FF2563EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1114,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1160,27 +1178,26 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1549,7 +1566,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2528,7 +2545,7 @@
         <v>111</v>
       </c>
       <c r="F21" s="11">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G21" s="12">
         <f>Parametres!$B$2+61</f>
@@ -2754,11 +2771,11 @@
       <c r="D26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="19" t="s">
-        <v>134</v>
+      <c r="E26" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="F26" s="11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G26" s="12">
         <f>Parametres!$B$2+68</f>
@@ -2772,7 +2789,7 @@
         <v>5</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>35</v>
@@ -2781,243 +2798,287 @@
         <v>36</v>
       </c>
       <c r="M26" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="W26" s="13"/>
+      <c r="X26" s="19"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="W26" s="20"/>
-      <c r="X26" s="21"/>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>139</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1</v>
+      </c>
+      <c r="G27" s="12">
+        <f>Parametres!$B$2+72</f>
+        <v>46262</v>
+      </c>
+      <c r="H27" s="12">
+        <f>Parametres!$B$2+76</f>
+        <v>46266</v>
+      </c>
+      <c r="I27" s="9">
+        <v>3</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F27" s="11">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12">
-        <f>Parametres!$B$2+75</f>
-        <v>46265</v>
-      </c>
-      <c r="H27" s="12">
-        <f>Parametres!$B$2+86</f>
-        <v>46276</v>
-      </c>
-      <c r="I27" s="9">
-        <v>10</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="X27" s="19"/>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M27" s="8" t="s">
+      <c r="B28" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-    </row>
-    <row r="28" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="D28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>144</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>140</v>
       </c>
       <c r="F28" s="11">
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <f>Parametres!$B$2+75</f>
-        <v>46265</v>
+        <f>Parametres!$B$2+77</f>
+        <v>46267</v>
       </c>
       <c r="H28" s="12">
-        <f>Parametres!$B$2+79</f>
-        <v>46269</v>
+        <f>Parametres!$B$2+90</f>
+        <v>46280</v>
       </c>
       <c r="I28" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J28" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="24"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C29" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <f>Parametres!$B$2+77</f>
+        <v>46267</v>
+      </c>
+      <c r="H29" s="12">
+        <f>Parametres!$B$2+83</f>
+        <v>46273</v>
+      </c>
+      <c r="I29" s="9">
+        <v>5</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="K29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="21"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F30" s="11">
         <v>1</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G30" s="12">
         <f>Parametres!$B$2+71</f>
         <v>46261</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H30" s="12">
         <f>Parametres!$B$2+71</f>
         <v>46261</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I30" s="9">
         <v>1</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="X29" s="25"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="K30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="X30" s="19"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F30" s="11">
+      <c r="E31" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="11">
         <v>0</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G31" s="12">
         <f>Parametres!$B$2+89</f>
         <v>46279</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H31" s="12">
         <f>Parametres!$B$2+93</f>
         <v>46283</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I31" s="9">
         <v>5</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="L30" s="9" t="s">
+      <c r="J31" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="L31" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M30" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="X30" s="14"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="26" t="s">
+      <c r="M31" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="X31" s="14"/>
+      <c r="Z31" s="21"/>
+      <c r="AA31" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="X31" s="28" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="30" t="s">
-        <v>161</v>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="X32" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-      <c r="B35" s="30" t="s">
-        <v>162</v>
+      <c r="A35" s="13"/>
+      <c r="B35" s="26" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="30" t="s">
-        <v>163</v>
+      <c r="A36" s="27"/>
+      <c r="B36" s="26" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="30" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
-        <v>165</v>
+      <c r="A37" s="21"/>
+      <c r="B37" s="26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="26" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="30" t="s">
-        <v>166</v>
+      <c r="B39" s="26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="26" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M30"/>
+  <autoFilter ref="A3:M31"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="A2:AA2"/>
@@ -3051,7 +3112,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3078,7 +3139,7 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3144,34 +3205,34 @@
         <v>14</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -3221,19 +3282,19 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>134</v>
+      <c r="E5" s="28" t="s">
+        <v>186</v>
       </c>
       <c r="F5" s="11">
         <v>0.89</v>
@@ -3253,36 +3314,36 @@
         <v>35</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="30" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>140</v>
+      <c r="E6" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F6" s="11">
         <v>0</v>
@@ -3299,7 +3360,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>35</v>
@@ -3308,26 +3369,26 @@
         <v>35</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="P6" s="14"/>
-      <c r="Q6" s="24"/>
+      <c r="Q6" s="21"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>140</v>
+      <c r="E7" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
@@ -3344,39 +3405,39 @@
         <v>45</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="P7" s="14"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="26" t="s">
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>140</v>
+      <c r="E8" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
@@ -3393,39 +3454,39 @@
         <v>45</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="P8" s="14"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="26" t="s">
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>140</v>
+      <c r="E9" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
@@ -3442,38 +3503,38 @@
         <v>35</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="P9" s="14"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="26" t="s">
+      <c r="U9" s="21"/>
+      <c r="V9" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>140</v>
+      <c r="E10" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="F10" s="11">
         <v>0</v>
@@ -3490,68 +3551,68 @@
         <v>25</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="P10" s="14"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="26" t="s">
+      <c r="V10" s="21"/>
+      <c r="W10" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="P11" s="28" t="s">
-        <v>159</v>
+      <c r="A11" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>160</v>
+      <c r="A13" s="25" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
-      <c r="B14" s="30" t="s">
-        <v>161</v>
+      <c r="B14" s="26" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="30" t="s">
-        <v>162</v>
+      <c r="A15" s="27"/>
+      <c r="B15" s="26" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="30" t="s">
-        <v>163</v>
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="30" t="s">
-        <v>164</v>
+      <c r="B17" s="26" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>165</v>
+      <c r="B18" s="26" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
-        <v>166</v>
+      <c r="B19" s="26" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3583,7 +3644,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3593,187 +3654,187 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>214</v>
+      <c r="A4" s="31" t="s">
+        <v>219</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="33">
+        <v>220</v>
+      </c>
+      <c r="C4" s="32">
         <f>Parametres!$B$2+8</f>
         <v>46198</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>219</v>
+      <c r="A5" s="31" t="s">
+        <v>224</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="33">
+        <v>225</v>
+      </c>
+      <c r="C5" s="32">
         <f>Parametres!$B$2+40</f>
         <v>46230</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>223</v>
+      <c r="A6" s="31" t="s">
+        <v>228</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C6" s="33">
+        <v>229</v>
+      </c>
+      <c r="C6" s="32">
         <f>Parametres!$B$2+63</f>
         <v>46253</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>228</v>
+      <c r="A7" s="33" t="s">
+        <v>233</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C7" s="33">
+        <v>234</v>
+      </c>
+      <c r="C7" s="32">
         <f>Parametres!$B$2+93</f>
         <v>46283</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>231</v>
+      <c r="A8" s="33" t="s">
+        <v>236</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="33">
+        <v>237</v>
+      </c>
+      <c r="C8" s="32">
         <f>Parametres!$B$2+156</f>
         <v>46346</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>234</v>
+      <c r="A9" s="33" t="s">
+        <v>239</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="33">
+        <v>240</v>
+      </c>
+      <c r="C9" s="32">
         <f>Parametres!$B$2+219</f>
         <v>46409</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>236</v>
+      <c r="A10" s="33" t="s">
+        <v>241</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="33">
+        <v>242</v>
+      </c>
+      <c r="C10" s="32">
         <f>Parametres!$B$2+268</f>
         <v>46458</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>238</v>
+      <c r="A11" s="33" t="s">
+        <v>243</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="C11" s="33">
+        <v>244</v>
+      </c>
+      <c r="C11" s="32">
         <f>Parametres!$B$2+303</f>
         <v>46493</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>35</v>
@@ -3790,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3800,296 +3861,303 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="35">
+        <v>249</v>
+      </c>
+      <c r="B2" s="34">
         <v>46190</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="B3" s="37">
-        <v>46262</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>247</v>
+      <c r="A3" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="36">
+        <v>46266</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="37">
+      <c r="A4" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="36">
         <v>46283</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>249</v>
+      <c r="C4" s="37" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>252</v>
+      <c r="A5" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>255</v>
+      <c r="A6" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="A7" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="A8" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="38" t="s">
+      <c r="A9" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="B10" s="36">
-        <v>26</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>259</v>
+      <c r="A10" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="35">
+        <v>27</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>262</v>
+      <c r="A11" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>265</v>
+      <c r="A12" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="36">
+      <c r="A13" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="35">
         <v>2</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>267</v>
+      <c r="C13" s="37" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="36">
+      <c r="A14" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="35">
         <v>3</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>269</v>
+      <c r="C14" s="37" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>272</v>
+      <c r="A15" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>275</v>
+      <c r="A16" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>278</v>
+      <c r="A17" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>279</v>
+      <c r="A20" s="39" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
+      <c r="A21" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
+      <c r="A22" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
+      <c r="A23" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
+      <c r="A24" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
+      <c r="A25" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
+      <c r="A26" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
-        <v>286</v>
-      </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
+      <c r="A27" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
+      <c r="A28" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
+      <c r="A29" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
+      <c r="A30" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
+      <c r="A31" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
+      <c r="A32" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
-        <v>292</v>
-      </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
+      <c r="A33" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
+      <c r="A34" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -4104,6 +4172,7 @@
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
